--- a/result/Table202603.xlsx
+++ b/result/Table202603.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5" t="n">
         <v>16.44</v>
       </c>
       <c r="J5" t="n">
-        <v>9.6</v>
+        <v>9.75</v>
       </c>
       <c r="K5" t="n">
-        <v>-41.61</v>
+        <v>-40.69</v>
       </c>
       <c r="L5" t="n">
-        <v>-41605.84</v>
+        <v>-40693.43</v>
       </c>
     </row>
     <row r="6">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
         <v>11.59</v>
       </c>
       <c r="J15" t="n">
-        <v>7.41</v>
+        <v>7.32</v>
       </c>
       <c r="K15" t="n">
-        <v>-36.07</v>
+        <v>-36.84</v>
       </c>
       <c r="L15" t="n">
-        <v>-36065.57</v>
+        <v>-36842.11</v>
       </c>
     </row>
     <row r="16">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I30" t="n">
         <v>24.89</v>
       </c>
       <c r="J30" t="n">
-        <v>18.28</v>
+        <v>17.69</v>
       </c>
       <c r="K30" t="n">
-        <v>-26.56</v>
+        <v>-28.93</v>
       </c>
       <c r="L30" t="n">
-        <v>-26556.85</v>
+        <v>-28927.28</v>
       </c>
     </row>
     <row r="31">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I46" t="n">
         <v>8.52</v>
       </c>
       <c r="J46" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.29</v>
+        <v>-51.88</v>
       </c>
       <c r="L46" t="n">
-        <v>-51291.08</v>
+        <v>-51877.93</v>
       </c>
     </row>
     <row r="47">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I47" t="n">
         <v>7.88</v>
       </c>
       <c r="J47" t="n">
-        <v>4.43</v>
+        <v>4.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-43.78</v>
+        <v>-44.54</v>
       </c>
       <c r="L47" t="n">
-        <v>-43781.73</v>
+        <v>-44543.15</v>
       </c>
     </row>
     <row r="48">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2807,19 +2807,19 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I49" t="n">
         <v>12.68</v>
       </c>
       <c r="J49" t="n">
-        <v>11.2</v>
+        <v>10.97</v>
       </c>
       <c r="K49" t="n">
-        <v>-11.67</v>
+        <v>-13.49</v>
       </c>
       <c r="L49" t="n">
-        <v>-11671.92</v>
+        <v>-13485.8</v>
       </c>
     </row>
     <row r="50">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3007,19 +3007,19 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I53" t="n">
         <v>82.72</v>
       </c>
       <c r="J53" t="n">
-        <v>62.73</v>
+        <v>61.17</v>
       </c>
       <c r="K53" t="n">
-        <v>-24.17</v>
+        <v>-26.05</v>
       </c>
       <c r="L53" t="n">
-        <v>-24165.86</v>
+        <v>-26051.74</v>
       </c>
     </row>
     <row r="54">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I56" t="n">
         <v>31.43</v>
       </c>
       <c r="J56" t="n">
-        <v>23.88</v>
+        <v>23.13</v>
       </c>
       <c r="K56" t="n">
-        <v>-24.02</v>
+        <v>-26.41</v>
       </c>
       <c r="L56" t="n">
-        <v>-24021.64</v>
+        <v>-26407.89</v>
       </c>
     </row>
     <row r="57">

--- a/result/Table202603.xlsx
+++ b/result/Table202603.xlsx
@@ -566,24 +566,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
         <v>42.09</v>
       </c>
       <c r="J3" t="n">
-        <v>44.36</v>
+        <v>41.32</v>
       </c>
       <c r="K3" t="n">
-        <v>5.39</v>
+        <v>-1.83</v>
       </c>
       <c r="L3" t="n">
-        <v>5393.21</v>
+        <v>-1829.41</v>
       </c>
     </row>
     <row r="4">
@@ -812,24 +812,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
         <v>6.07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.76</v>
+        <v>6.07</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.11</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-5107.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I16" t="n">
         <v>52.22</v>
       </c>
       <c r="J16" t="n">
-        <v>49.18</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.82</v>
+        <v>34.87</v>
       </c>
       <c r="L16" t="n">
-        <v>-5821.52</v>
+        <v>34871.7</v>
       </c>
     </row>
     <row r="17">
@@ -1396,24 +1396,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>45.87</v>
       </c>
       <c r="J20" t="n">
-        <v>43.11</v>
+        <v>40.98</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.02</v>
+        <v>-10.66</v>
       </c>
       <c r="L20" t="n">
-        <v>-6017</v>
+        <v>-10660.56</v>
       </c>
     </row>
     <row r="21">
@@ -1492,24 +1492,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>8.99</v>
       </c>
       <c r="J22" t="n">
-        <v>8.609999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.23</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-4226.92</v>
+        <v>-9454.950000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1588,24 +1588,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I24" t="n">
         <v>3.88</v>
       </c>
       <c r="J24" t="n">
-        <v>5.17</v>
+        <v>6.01</v>
       </c>
       <c r="K24" t="n">
-        <v>33.25</v>
+        <v>54.9</v>
       </c>
       <c r="L24" t="n">
-        <v>33247.42</v>
+        <v>54896.91</v>
       </c>
     </row>
     <row r="25">
@@ -1830,24 +1830,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>2.22</v>
       </c>
       <c r="J29" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.01</v>
+        <v>-3.15</v>
       </c>
       <c r="L29" t="n">
-        <v>-9009.01</v>
+        <v>-3153.15</v>
       </c>
     </row>
     <row r="30">
@@ -2226,24 +2226,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
         <v>58.54</v>
       </c>
       <c r="J37" t="n">
-        <v>53.78</v>
+        <v>60.14</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.130000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="L37" t="n">
-        <v>-8131.19</v>
+        <v>2733.17</v>
       </c>
     </row>
     <row r="38">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
         <v>9.779999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>9.94</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>1.64</v>
+        <v>-4.19</v>
       </c>
       <c r="L39" t="n">
-        <v>1635.99</v>
+        <v>-4192.23</v>
       </c>
     </row>
     <row r="40">
@@ -2364,24 +2364,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
         <v>19.65</v>
       </c>
       <c r="J40" t="n">
-        <v>20.22</v>
+        <v>19.47</v>
       </c>
       <c r="K40" t="n">
-        <v>2.9</v>
+        <v>-0.92</v>
       </c>
       <c r="L40" t="n">
-        <v>2900.76</v>
+        <v>-916.03</v>
       </c>
     </row>
     <row r="41">
@@ -2506,24 +2506,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
         <v>5.29</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.48</v>
+        <v>19.66</v>
       </c>
       <c r="L43" t="n">
-        <v>-5482.04</v>
+        <v>19659.74</v>
       </c>
     </row>
     <row r="44">
@@ -2552,24 +2552,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I44" t="n">
         <v>11.98</v>
       </c>
       <c r="J44" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.18</v>
+        <v>-6.09</v>
       </c>
       <c r="L44" t="n">
-        <v>-8180.3</v>
+        <v>-6093.49</v>
       </c>
     </row>
     <row r="45">
@@ -3448,24 +3448,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I62" t="n">
         <v>57.89</v>
       </c>
       <c r="J62" t="n">
-        <v>70.84</v>
+        <v>69.91</v>
       </c>
       <c r="K62" t="n">
-        <v>22.37</v>
+        <v>20.76</v>
       </c>
       <c r="L62" t="n">
-        <v>22370.01</v>
+        <v>20763.52</v>
       </c>
     </row>
     <row r="63">
@@ -3544,24 +3544,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I64" t="n">
         <v>16.1</v>
       </c>
       <c r="J64" t="n">
-        <v>14.94</v>
+        <v>14.23</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.2</v>
+        <v>-11.61</v>
       </c>
       <c r="L64" t="n">
-        <v>-7204.97</v>
+        <v>-11614.91</v>
       </c>
     </row>
     <row r="65">
@@ -3740,24 +3740,24 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I68" t="n">
         <v>64.38</v>
       </c>
       <c r="J68" t="n">
-        <v>59.49</v>
+        <v>56.69</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.6</v>
+        <v>-11.94</v>
       </c>
       <c r="L68" t="n">
-        <v>-7595.53</v>
+        <v>-11944.7</v>
       </c>
     </row>
     <row r="69">
@@ -3886,24 +3886,24 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I71" t="n">
         <v>21.68</v>
       </c>
       <c r="J71" t="n">
-        <v>20.18</v>
+        <v>19.38</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.92</v>
+        <v>-10.61</v>
       </c>
       <c r="L71" t="n">
-        <v>-6918.82</v>
+        <v>-10608.86</v>
       </c>
     </row>
     <row r="72">
@@ -3982,24 +3982,24 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
         <v>19.33</v>
       </c>
       <c r="J73" t="n">
-        <v>18.1</v>
+        <v>17.06</v>
       </c>
       <c r="K73" t="n">
-        <v>-6.36</v>
+        <v>-11.74</v>
       </c>
       <c r="L73" t="n">
-        <v>-6363.17</v>
+        <v>-11743.4</v>
       </c>
     </row>
     <row r="74">
@@ -4028,24 +4028,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I74" t="n">
         <v>48.83</v>
       </c>
       <c r="J74" t="n">
-        <v>55.86</v>
+        <v>60.27</v>
       </c>
       <c r="K74" t="n">
-        <v>14.4</v>
+        <v>23.43</v>
       </c>
       <c r="L74" t="n">
-        <v>14396.89</v>
+        <v>23428.22</v>
       </c>
     </row>
     <row r="75">

--- a/result/Table202603.xlsx
+++ b/result/Table202603.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="n">
         <v>16.44</v>
       </c>
       <c r="J5" t="n">
-        <v>9.75</v>
+        <v>9.56</v>
       </c>
       <c r="K5" t="n">
-        <v>-40.69</v>
+        <v>-41.85</v>
       </c>
       <c r="L5" t="n">
-        <v>-40693.43</v>
+        <v>-41849.15</v>
       </c>
     </row>
     <row r="6">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I15" t="n">
         <v>11.59</v>
       </c>
       <c r="J15" t="n">
-        <v>7.32</v>
+        <v>7.19</v>
       </c>
       <c r="K15" t="n">
-        <v>-36.84</v>
+        <v>-37.96</v>
       </c>
       <c r="L15" t="n">
-        <v>-36842.11</v>
+        <v>-37963.76</v>
       </c>
     </row>
     <row r="16">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I30" t="n">
         <v>24.89</v>
       </c>
       <c r="J30" t="n">
-        <v>17.69</v>
+        <v>17.06</v>
       </c>
       <c r="K30" t="n">
-        <v>-28.93</v>
+        <v>-31.46</v>
       </c>
       <c r="L30" t="n">
-        <v>-28927.28</v>
+        <v>-31458.42</v>
       </c>
     </row>
     <row r="31">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I46" t="n">
         <v>8.52</v>
       </c>
       <c r="J46" t="n">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.88</v>
+        <v>-52.7</v>
       </c>
       <c r="L46" t="n">
-        <v>-51877.93</v>
+        <v>-52699.53</v>
       </c>
     </row>
     <row r="47">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I47" t="n">
         <v>7.88</v>
       </c>
       <c r="J47" t="n">
-        <v>4.37</v>
+        <v>4.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-44.54</v>
+        <v>-46.45</v>
       </c>
       <c r="L47" t="n">
-        <v>-44543.15</v>
+        <v>-46446.7</v>
       </c>
     </row>
     <row r="48">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2807,19 +2807,19 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I49" t="n">
         <v>12.68</v>
       </c>
       <c r="J49" t="n">
-        <v>10.97</v>
+        <v>12.12</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.49</v>
+        <v>-4.42</v>
       </c>
       <c r="L49" t="n">
-        <v>-13485.8</v>
+        <v>-4416.4</v>
       </c>
     </row>
     <row r="50">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3007,19 +3007,19 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I53" t="n">
         <v>82.72</v>
       </c>
       <c r="J53" t="n">
-        <v>61.17</v>
+        <v>61.56</v>
       </c>
       <c r="K53" t="n">
-        <v>-26.05</v>
+        <v>-25.58</v>
       </c>
       <c r="L53" t="n">
-        <v>-26051.74</v>
+        <v>-25580.27</v>
       </c>
     </row>
     <row r="54">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I56" t="n">
         <v>31.43</v>
       </c>
       <c r="J56" t="n">
-        <v>23.13</v>
+        <v>22.99</v>
       </c>
       <c r="K56" t="n">
-        <v>-26.41</v>
+        <v>-26.85</v>
       </c>
       <c r="L56" t="n">
-        <v>-26407.89</v>
+        <v>-26853.32</v>
       </c>
     </row>
     <row r="57">

--- a/result/Table202603.xlsx
+++ b/result/Table202603.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I5" t="n">
         <v>16.44</v>
       </c>
       <c r="J5" t="n">
-        <v>9.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-41.85</v>
+        <v>-44.04</v>
       </c>
       <c r="L5" t="n">
-        <v>-41849.15</v>
+        <v>-44038.93</v>
       </c>
     </row>
     <row r="6">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I15" t="n">
         <v>11.59</v>
       </c>
       <c r="J15" t="n">
-        <v>7.19</v>
+        <v>7.06</v>
       </c>
       <c r="K15" t="n">
-        <v>-37.96</v>
+        <v>-39.09</v>
       </c>
       <c r="L15" t="n">
-        <v>-37963.76</v>
+        <v>-39085.42</v>
       </c>
     </row>
     <row r="16">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
         <v>24.89</v>
       </c>
       <c r="J30" t="n">
-        <v>17.06</v>
+        <v>15.73</v>
       </c>
       <c r="K30" t="n">
-        <v>-31.46</v>
+        <v>-36.8</v>
       </c>
       <c r="L30" t="n">
-        <v>-31458.42</v>
+        <v>-36801.93</v>
       </c>
     </row>
     <row r="31">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I46" t="n">
         <v>8.52</v>
       </c>
       <c r="J46" t="n">
-        <v>4.03</v>
+        <v>3.78</v>
       </c>
       <c r="K46" t="n">
-        <v>-52.7</v>
+        <v>-55.63</v>
       </c>
       <c r="L46" t="n">
-        <v>-52699.53</v>
+        <v>-55633.8</v>
       </c>
     </row>
     <row r="47">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I47" t="n">
         <v>7.88</v>
       </c>
       <c r="J47" t="n">
-        <v>4.22</v>
+        <v>4.04</v>
       </c>
       <c r="K47" t="n">
-        <v>-46.45</v>
+        <v>-48.73</v>
       </c>
       <c r="L47" t="n">
-        <v>-46446.7</v>
+        <v>-48730.96</v>
       </c>
     </row>
     <row r="48">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2807,19 +2807,19 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I49" t="n">
         <v>12.68</v>
       </c>
       <c r="J49" t="n">
-        <v>12.12</v>
+        <v>12.55</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.42</v>
+        <v>-1.03</v>
       </c>
       <c r="L49" t="n">
-        <v>-4416.4</v>
+        <v>-1025.24</v>
       </c>
     </row>
     <row r="50">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3007,19 +3007,19 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I53" t="n">
         <v>82.72</v>
       </c>
       <c r="J53" t="n">
-        <v>61.56</v>
+        <v>58.01</v>
       </c>
       <c r="K53" t="n">
-        <v>-25.58</v>
+        <v>-29.87</v>
       </c>
       <c r="L53" t="n">
-        <v>-25580.27</v>
+        <v>-29871.86</v>
       </c>
     </row>
     <row r="54">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I56" t="n">
         <v>31.43</v>
       </c>
       <c r="J56" t="n">
-        <v>22.99</v>
+        <v>22.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-26.85</v>
+        <v>-27.52</v>
       </c>
       <c r="L56" t="n">
-        <v>-26853.32</v>
+        <v>-27521.48</v>
       </c>
     </row>
     <row r="57">

--- a/result/Table202603.xlsx
+++ b/result/Table202603.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I5" t="n">
         <v>16.44</v>
       </c>
       <c r="J5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-44.04</v>
+        <v>-44.4</v>
       </c>
       <c r="L5" t="n">
-        <v>-44038.93</v>
+        <v>-44403.89</v>
       </c>
     </row>
     <row r="6">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I15" t="n">
         <v>11.59</v>
       </c>
       <c r="J15" t="n">
-        <v>7.06</v>
+        <v>6.92</v>
       </c>
       <c r="K15" t="n">
-        <v>-39.09</v>
+        <v>-40.29</v>
       </c>
       <c r="L15" t="n">
-        <v>-39085.42</v>
+        <v>-40293.36</v>
       </c>
     </row>
     <row r="16">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I30" t="n">
         <v>24.89</v>
       </c>
       <c r="J30" t="n">
-        <v>15.73</v>
+        <v>15.65</v>
       </c>
       <c r="K30" t="n">
-        <v>-36.8</v>
+        <v>-37.12</v>
       </c>
       <c r="L30" t="n">
-        <v>-36801.93</v>
+        <v>-37123.34</v>
       </c>
     </row>
     <row r="31">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I46" t="n">
         <v>8.52</v>
       </c>
       <c r="J46" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="K46" t="n">
-        <v>-55.63</v>
+        <v>-55.16</v>
       </c>
       <c r="L46" t="n">
-        <v>-55633.8</v>
+        <v>-55164.32</v>
       </c>
     </row>
     <row r="47">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I47" t="n">
         <v>7.88</v>
       </c>
       <c r="J47" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="K47" t="n">
-        <v>-48.73</v>
+        <v>-48.6</v>
       </c>
       <c r="L47" t="n">
-        <v>-48730.96</v>
+        <v>-48604.06</v>
       </c>
     </row>
     <row r="48">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2807,19 +2807,19 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I49" t="n">
         <v>12.68</v>
       </c>
       <c r="J49" t="n">
-        <v>12.55</v>
+        <v>12.76</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.03</v>
+        <v>0.63</v>
       </c>
       <c r="L49" t="n">
-        <v>-1025.24</v>
+        <v>630.91</v>
       </c>
     </row>
     <row r="50">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3007,19 +3007,19 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I53" t="n">
         <v>82.72</v>
       </c>
       <c r="J53" t="n">
-        <v>58.01</v>
+        <v>61.43</v>
       </c>
       <c r="K53" t="n">
-        <v>-29.87</v>
+        <v>-25.74</v>
       </c>
       <c r="L53" t="n">
-        <v>-29871.86</v>
+        <v>-25737.43</v>
       </c>
     </row>
     <row r="54">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I56" t="n">
         <v>31.43</v>
       </c>
       <c r="J56" t="n">
-        <v>22.78</v>
+        <v>22.84</v>
       </c>
       <c r="K56" t="n">
-        <v>-27.52</v>
+        <v>-27.33</v>
       </c>
       <c r="L56" t="n">
-        <v>-27521.48</v>
+        <v>-27330.58</v>
       </c>
     </row>
     <row r="57">
